--- a/stories/arbres/ATOM-LAN.MOT.001-07.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Éloi tient la main de maman au marché. Une poire. Une fraise. Un bonnet. Une chaussette. Maman dit : on nomme. On classe. Une catégorie pour les fruits. Une catégorie pour les habits. Éloi met la poire et la fraise dans le filet. Catégorie des fruits. Il met le bonnet et la chaussette dans le sac. Catégorie des habits.</t>
+          <t>Éloi tient la main de maman au marché. Une poire. Une fraise. Un bonnet. Une chaussette. On nomme. On classe. Une catégorie pour les fruits. Une catégorie pour les habits. Éloi met la poire et la fraise dans le filet. Catégorie des fruits. Il met le bonnet et la chaussette dans le sac. Catégorie des habits.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Éloi tient la main de maman au marché. Une poire. Une fraise. Un bonnet. Une chaussette.
+maman|On nomme. On classe.
+narrateur|Une catégorie pour les fruits. Une catégorie pour les habits. Éloi met la poire et la fraise dans le filet. Catégorie des fruits. Il met le bonnet et la chaussette dans le sac. Catégorie des habits.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Éloi range poire et bonnet. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Éloi a classé. Une catégorie pour les fruits. Une pour les habits.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1824,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman paie. Éloi tient le filet.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1991,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2031,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.MOT.001-07.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Une catégorie pour les fruits. Une catégorie pour les habits. Éloi met la poire et la fraise dans le filet. Catégorie des fruits. Il met le bonnet et la chaussette dans le sac. Catégorie des habits.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1501,7 @@
           <t>narrateur|Éloi range poire et bonnet. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1673,7 @@
           <t>narrateur|Éloi a classé. Une catégorie pour les fruits. Une pour les habits.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1837,7 @@
           <t>narrateur|Maman paie. Éloi tient le filet.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1996,6 +2005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2014,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2038,6 +2048,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2239,6 +2263,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-LAN.MOT.001-07.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Éloi classe au marché</t>
+          <t>Les toiles et le filet d'Aniss</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sous les toiles du marché, Aniss tient le filet. Il nomme poire et fraise, bonnet et chaussette, puis range deux catégories.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Éloi tient la main de maman au marché. Une poire. Une fraise. Un bonnet. Une chaussette. On nomme. On classe. Une catégorie pour les fruits. Une catégorie pour les habits. Éloi met la poire et la fraise dans le filet. Catégorie des fruits. Il met le bonnet et la chaussette dans le sac. Catégorie des habits.</t>
+          <t>Les toiles du marché claquent un peu. Ça sent la fraise, tout proche. Un pigeon picore une miette. Les pavés sont encore humides. Un filet vide pend au poignet de maman. Une voix loin dit le prix des poires. Aniss, tu sens les fraises ? Oui, maman. C'est sucré, déjà, dans l'air. On a pris des fruits. Et aussi des habits, au stand d'à côté. En ce moment, Aniss tient la main de maman. Sa main est tiède, un peu rêche. Sur le banc du stand : une poire. Une fraise. Un bonnet. Une chaussette. La poire est verte, un peu dure. On nomme. On classe. Une catégorie pour les fruits. Une catégorie pour les habits. Aniss prend la poire. Poire. C'est un fruit. Mets-la dans le filet. Aniss glisse la poire dans le filet. Le filet s'étire, tout doux. Il prend la fraise. Elle est rouge, un peu molle du bout. Fraise. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Aniss met la fraise avec la poire. Il prend le bonnet de laine. Le bonnet sent encore un peu le stand. Bonnet. C'est un habit. Oui. Le sac est ici, à côté. Aniss pose le bonnet dans le sac. Il prend la chaussette neuve. Elle est encore un peu raide. Chaussette. C'est un habit. Les habits ensemble. C'est une catégorie. Aniss met la chaussette avec le bonnet. Catégorie. Fruits dans le filet. Habits dans le sac. Bravo, Aniss. Tu as nommé. Tu as classé. Tu as mis ensemble. C'est du bon travail. Tu as fini de ranger le stand ? Oui, maman. Le filet a les fruits. Le sac a les habits. Le pigeon a fini sa miette. On va payer, puis on rentre. Je tiens le filet.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,9 +1324,70 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Éloi tient la main de maman au marché. Une poire. Une fraise. Un bonnet. Une chaussette.
-maman|On nomme. On classe.
-narrateur|Une catégorie pour les fruits. Une catégorie pour les habits. Éloi met la poire et la fraise dans le filet. Catégorie des fruits. Il met le bonnet et la chaussette dans le sac. Catégorie des habits.</t>
+          <t>narrateur|Les toiles du marché claquent un peu.
+narrateur|Ça sent la fraise, tout proche.
+narrateur|Un pigeon picore une miette.
+narrateur|Les pavés sont encore humides.
+narrateur|Un filet vide pend au poignet de maman.
+narrateur|Une voix loin dit le prix des poires.
+maman|Aniss, tu sens les fraises ?
+enfant-m|Oui, maman.
+enfant-m|C'est sucré, déjà, dans l'air.
+maman|On a pris des fruits.
+maman|Et aussi des habits, au stand d'à côté.
+narrateur|En ce moment, Aniss tient la main de maman.
+narrateur|Sa main est tiède, un peu rêche.
+narrateur|Sur le banc du stand : une poire.
+narrateur|Une fraise.
+narrateur|Un bonnet.
+narrateur|Une chaussette.
+enfant-m|La poire est verte, un peu dure.
+maman|On nomme.
+maman|On classe.
+maman|Une catégorie pour les fruits.
+maman|Une catégorie pour les habits.
+narrateur|Aniss prend la poire.
+enfant-m|Poire.
+enfant-m|C'est un fruit.
+maman|Mets-la dans le filet.
+narrateur|Aniss glisse la poire dans le filet.
+narrateur|Le filet s'étire, tout doux.
+narrateur|Il prend la fraise.
+narrateur|Elle est rouge, un peu molle du bout.
+enfant-m|Fraise.
+enfant-m|C'est un fruit aussi.
+maman|Les fruits ensemble.
+maman|C'est une catégorie.
+narrateur|Aniss met la fraise avec la poire.
+narrateur|Il prend le bonnet de laine.
+narrateur|Le bonnet sent encore un peu le stand.
+enfant-m|Bonnet.
+enfant-m|C'est un habit.
+maman|Oui.
+maman|Le sac est ici, à côté.
+narrateur|Aniss pose le bonnet dans le sac.
+narrateur|Il prend la chaussette neuve.
+narrateur|Elle est encore un peu raide.
+enfant-m|Chaussette.
+enfant-m|C'est un habit.
+maman|Les habits ensemble.
+maman|C'est une catégorie.
+narrateur|Aniss met la chaussette avec le bonnet.
+enfant-m|Catégorie.
+enfant-m|Fruits dans le filet.
+enfant-m|Habits dans le sac.
+maman|Bravo, Aniss.
+maman|Tu as nommé.
+maman|Tu as classé.
+maman|Tu as mis ensemble.
+maman|C'est du bon travail.
+maman|Tu as fini de ranger le stand ?
+enfant-m|Oui, maman.
+narrateur|Le filet a les fruits.
+narrateur|Le sac a les habits.
+narrateur|Le pigeon a fini sa miette.
+maman|On va payer, puis on rentre.
+enfant-m|Je tiens le filet.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1342,7 +1415,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Éloi range poire et bonnet. Que fait-il ?</t>
+          <t>Aniss range poire et bonnet. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1498,7 +1571,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Éloi range poire et bonnet. Que fait-il ?</t>
+          <t>narrateur|Aniss range poire et bonnet.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1526,7 +1600,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Éloi a classé. Une catégorie pour les fruits. Une pour les habits.</t>
+          <t>Aniss a classé. Une catégorie pour les fruits. Une pour les habits. Tu as mis ensemble. Bravo. C'est du bon travail, Aniss. Le filet est prêt ? Oui. Les fruits sont ensemble. Et les habits ? Dans le sac. Les toiles claquent encore, plus loin. Ça sent toujours la fraise.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1670,7 +1744,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Éloi a classé. Une catégorie pour les fruits. Une pour les habits.</t>
+          <t>narrateur|Aniss a classé.
+narrateur|Une catégorie pour les fruits.
+narrateur|Une pour les habits.
+maman|Tu as mis ensemble.
+maman|Bravo.
+maman|C'est du bon travail, Aniss.
+maman|Le filet est prêt ?
+enfant-m|Oui.
+enfant-m|Les fruits sont ensemble.
+maman|Et les habits ?
+enfant-m|Dans le sac.
+narrateur|Les toiles claquent encore, plus loin.
+narrateur|Ça sent toujours la fraise.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1698,7 +1784,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman paie. Éloi tient le filet.</t>
+          <t>Maman paie, tout calme. Les pièces font un petit bruit clair. Tu tiens le filet ? Oui, maman. Aniss tient le filet contre son ventre. Les fruits bougent un peu, tout doux. Le sac des habits est sur mon épaule. Deux catégories. On rentre par la rue mouillée. Les pavés brillent. Un pigeon s'envole, tout près. Tu as classé au marché. Puis on rentre. Le filet tape un peu le manteau.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1834,7 +1920,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman paie. Éloi tient le filet.</t>
+          <t>narrateur|Maman paie, tout calme.
+narrateur|Les pièces font un petit bruit clair.
+maman|Tu tiens le filet ?
+enfant-m|Oui, maman.
+narrateur|Aniss tient le filet contre son ventre.
+narrateur|Les fruits bougent un peu, tout doux.
+maman|Le sac des habits est sur mon épaule.
+enfant-m|Deux catégories.
+maman|On rentre par la rue mouillée.
+narrateur|Les pavés brillent.
+narrateur|Un pigeon s'envole, tout près.
+maman|Tu as classé au marché.
+enfant-m|Puis on rentre.
+narrateur|Le filet tape un peu le manteau.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1862,7 +1961,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai classé. Fruits. Habits. Bravo. Tu as fait du bon travail. Les toiles du marché s'éloignent. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2002,7 +2101,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai classé.
+enfant-m|Fruits.
+enfant-m|Habits.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Les toiles du marché s'éloignent.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2024,7 +2129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2062,6 +2167,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.MOT.001-07.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-07.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les toiles du marché claquent un peu. Ça sent la fraise, tout proche. Un pigeon picore une miette. Les pavés sont encore humides. Un filet vide pend au poignet de maman. Une voix loin dit le prix des poires. Aniss, tu sens les fraises ? Oui, maman. C'est sucré, déjà, dans l'air. On a pris des fruits. Et aussi des habits, au stand d'à côté. En ce moment, Aniss tient la main de maman. Sa main est tiède, un peu rêche. Sur le banc du stand : une poire. Une fraise. Un bonnet. Une chaussette. La poire est verte, un peu dure. On nomme. On classe. Une catégorie pour les fruits. Une catégorie pour les habits. Aniss prend la poire. Poire. C'est un fruit. Mets-la dans le filet. Aniss glisse la poire dans le filet. Le filet s'étire, tout doux. Il prend la fraise. Elle est rouge, un peu molle du bout. Fraise. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Aniss met la fraise avec la poire. Il prend le bonnet de laine. Le bonnet sent encore un peu le stand. Bonnet. C'est un habit. Oui. Le sac est ici, à côté. Aniss pose le bonnet dans le sac. Il prend la chaussette neuve. Elle est encore un peu raide. Chaussette. C'est un habit. Les habits ensemble. C'est une catégorie. Aniss met la chaussette avec le bonnet. Catégorie. Fruits dans le filet. Habits dans le sac. Bravo, Aniss. Tu as nommé. Tu as classé. Tu as mis ensemble. C'est du bon travail. Tu as fini de ranger le stand ? Oui, maman. Le filet a les fruits. Le sac a les habits. Le pigeon a fini sa miette. On va payer, puis on rentre. Je tiens le filet.</t>
+          <t>Les toiles du marché claquent un peu. Ça sent la fraise, tout proche. Un pigeon picore une miette. Les pavés sont encore humides. Un filet vide pend au poignet de maman. Une voix loin dit le prix des poires. Aniss, tu sens les fraises ? Oui, maman. C'est sucré, déjà, dans l'air. On a pris des fruits. Et aussi des habits, au stand d'à côté. En ce moment, Aniss tient la main de maman. Sa main est tiède, un peu rêche. Sur le banc du stand : une poire. Une fraise. Un bonnet. Une chaussette. La poire est verte, un peu dure. On nomme. On classe. Une catégorie pour les fruits. Une catégorie pour les habits. Aniss prend la poire. Poire. C'est un fruit. Mets-la dans le filet. Aniss glisse la poire dans le filet. Le filet s'étire, tout doux. Il prend la fraise. Elle est rouge, un peu molle du bout. Fraise. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Aniss met la fraise avec la poire. Il prend le bonnet de laine. Le bonnet sent encore un peu le stand. Bonnet. C'est un habit. Oui. Le sac est ici, à côté. Aniss pose le bonnet dans le sac. Il prend la chaussette neuve. Elle est encore un peu raide. Chaussette. C'est un habit. Les habits ensemble. C'est une catégorie. Aniss met la chaussette avec le bonnet. Catégorie. Fruits dans le filet. Habits dans le sac. Bravo, Aniss. Tu as nommé. Tu as classé. Tu as mis ensemble. Tu as fini de ranger le stand ? Oui, maman. Le filet a les fruits. Le sac a les habits. Le pigeon a fini sa miette. On va payer, puis on rentre. Je tiens le filet.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Éloi tient la main de maman au marché. Une poire. Une fraise. Un bonnet. Une chaussette. Maman dit : on nomme. On classe. Une &lt;emphasis level="moderate"&gt;catégorie&lt;/emphasis&gt; pour les fruits. Une catégorie pour les habits. Éloi met la poire et la fraise dans le filet. Catégorie des fruits. Il met le bonnet et la chaussette dans le sac. Catégorie des habits.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les toiles du marché claquent un peu. Ça sent la fraise, tout proche. Un pigeon picore une miette. Les pavés sont encore humides. Un filet vide pend au poignet de maman. Une voix loin dit le prix des poires. Aniss, tu sens les fraises ? Oui, maman. C'est sucré, déjà, dans l'air. On a pris des fruits. Et aussi des habits, au stand d'à côté. En ce moment, Aniss tient la main de maman. Sa main est tiède, un peu rêche. Sur le banc du stand : une poire. Une fraise. Un bonnet. Une chaussette. La poire est verte, un peu dure. On nomme. On classe. Une catégorie pour les fruits. Une catégorie pour les habits. Aniss prend la poire. Poire. C'est un fruit. Mets-la dans le filet. Aniss glisse la poire dans le filet. Le filet s'étire, tout doux. Il prend la fraise. Elle est rouge, un peu molle du bout. Fraise. C'est un fruit aussi. Les fruits ensemble. C'est une catégorie. Aniss met la fraise avec la poire. Il prend le bonnet de laine. Le bonnet sent encore un peu le stand. Bonnet. C'est un habit. Oui. Le sac est ici, à côté. Aniss pose le bonnet dans le sac. Il prend la chaussette neuve. Elle est encore un peu raide. Chaussette. C'est un habit. Les habits ensemble. C'est une catégorie. Aniss met la chaussette avec le bonnet. Catégorie. Fruits dans le filet. Habits dans le sac. Bravo, Aniss. Tu as nommé. Tu as classé. Tu as mis ensemble. Tu as fini de ranger le stand ? Oui, maman. Le filet a les fruits. Le sac a les habits. Le pigeon a fini sa miette. On va payer, puis on rentre. Je tiens le filet.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1380,7 +1380,6 @@
 maman|Tu as nommé.
 maman|Tu as classé.
 maman|Tu as mis ensemble.
-maman|C'est du bon travail.
 maman|Tu as fini de ranger le stand ?
 enfant-m|Oui, maman.
 narrateur|Le filet a les fruits.
@@ -1390,7 +1389,6 @@
 enfant-m|Je tiens le filet.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1420,7 +1418,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Éloi range poire et bonnet. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss range poire et bonnet. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1575,7 +1573,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1600,12 +1597,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aniss a classé. Une catégorie pour les fruits. Une pour les habits. Tu as mis ensemble. Bravo. C'est du bon travail, Aniss. Le filet est prêt ? Oui. Les fruits sont ensemble. Et les habits ? Dans le sac. Les toiles claquent encore, plus loin. Ça sent toujours la fraise.</t>
+          <t>Aniss a classé. Une catégorie pour les fruits. Une pour les habits. Tu as mis ensemble. Bravo. Le filet est prêt ? Oui. Les fruits sont ensemble. Et les habits ? Dans le sac. Les toiles claquent encore, plus loin. Ça sent toujours la fraise.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Éloi a classé. Une &lt;emphasis level="moderate"&gt;catégorie&lt;/emphasis&gt; pour les fruits. Une pour les habits.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss a classé. Une catégorie pour les fruits. Une pour les habits. Tu as mis ensemble. Bravo. Le filet est prêt ? Oui. Les fruits sont ensemble. Et les habits ? Dans le sac. Les toiles claquent encore, plus loin. Ça sent toujours la fraise.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1749,7 +1746,6 @@
 narrateur|Une pour les habits.
 maman|Tu as mis ensemble.
 maman|Bravo.
-maman|C'est du bon travail, Aniss.
 maman|Le filet est prêt ?
 enfant-m|Oui.
 enfant-m|Les fruits sont ensemble.
@@ -1759,7 +1755,6 @@
 narrateur|Ça sent toujours la fraise.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1789,7 +1784,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman paie. Éloi tient le filet.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman paie, tout calme. Les pièces font un petit bruit clair. Tu tiens le filet ? Oui, maman. Aniss tient le filet contre son ventre. Les fruits bougent un peu, tout doux. Le sac des habits est sur mon épaule. Deux catégories. On rentre par la rue mouillée. Les pavés brillent. Un pigeon s'envole, tout près. Tu as classé au marché. Puis on rentre. Le filet tape un peu le manteau.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1936,7 +1931,6 @@
 narrateur|Le filet tape un peu le manteau.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,12 +1955,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai classé. Fruits. Habits. Bravo. Tu as fait du bon travail. Les toiles du marché s'éloignent. L'histoire est finie.</t>
+          <t>J'ai classé. Fruits. Habits. Bravo. Les toiles du marché s'éloignent.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai classé. Fruits. Habits. Bravo. Les toiles du marché s'éloignent.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2105,12 +2099,9 @@
 enfant-m|Fruits.
 enfant-m|Habits.
 maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Les toiles du marché s'éloignent.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Les toiles du marché s'éloignent.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2129,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2174,6 +2165,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.MOT.001-07.xlsx
+++ b/stories/arbres/ATOM-LAN.MOT.001-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Éloi, maman</t>
+          <t>Aniss, maman</t>
         </is>
       </c>
     </row>
